--- a/Lich_Dang_Bai_SEO_ThueXeCarnival.xlsx
+++ b/Lich_Dang_Bai_SEO_ThueXeCarnival.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Đã viết xong - sẵn sàng đăng</t>
+          <t>Đã đăng</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">

--- a/Lich_Dang_Bai_SEO_ThueXeCarnival.xlsx
+++ b/Lich_Dang_Bai_SEO_ThueXeCarnival.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1079,6 +1079,117 @@
       <c r="G16" s="4" t="inlineStr">
         <is>
           <t>thue-xe-carnival-di-cong-tac-tinh.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Thuê Xe Carnival Đi Phan Thiết Tự Túc</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>thuê xe Carnival đi Phan Thiết</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-di-phan-thiet.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Thuê Xe Carnival Đi Tây Ninh, Núi Bà Đen Trong Ngày</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>thuê xe Carnival đi Tây Ninh Núi Bà Đen</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-di-tay-ninh.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Thuê Xe Carnival Đi Nha Trang Đường Dài</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>thuê xe Carnival đi Nha Trang</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-di-nha-trang.html</t>
         </is>
       </c>
     </row>

--- a/Lich_Dang_Bai_SEO_ThueXeCarnival.xlsx
+++ b/Lich_Dang_Bai_SEO_ThueXeCarnival.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1190,6 +1190,598 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>kinh-nghiem-thue-xe-di-nha-trang.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gia Đình Đông Người: Nên Thuê 1 Xe Carnival Hay 2 Xe Nhỏ?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>nên thuê 1 xe hay 2 xe cho gia đình đông người</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>nen-thue-1-xe-carnival-hay-2-xe-nho.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Thuê Xe Carnival Về Quê Dịp Tết Nguyên Đán</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>thuê xe về quê Tết</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-ve-que-tet.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Thuê Xe Carnival Đón Đối Tác, Khách VIP Tại Sân Bay</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>thuê xe đón đối tác VIP sân bay</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Dịch vụ đặc biệt</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>thue-xe-carnival-don-doi-tac-vip-san-bay.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Thuê Xe 7 Chỗ Đi Bến Tre Từ TP.HCM: Lịch Trình 1 Ngày Xứ Dừa</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>thuê xe 7 chỗ đi Bến Tre</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-di-ben-tre.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Thuê Xe Carnival Đi Cửa Khẩu Mộc Bài: Giá, Lộ Trình Và Lưu Ý Qua Biên</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>thuê xe đi cửa khẩu Mộc Bài</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>thue-xe-carnival-di-cua-khau-moc-bai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Thuê Xe Carnival Đi Rạch Giá, Nối Chuyến Tàu Ra Phú Quốc</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>thuê xe đi Rạch Giá</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-di-rach-gia.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Thuê Xe Carnival Đi Bạc Liêu – Cà Mau Về Đất Mũi</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>thuê xe đi Cà Mau Bạc Liêu</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-di-bac-lieu-ca-mau.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Thuê Xe Carnival Đi Châu Đốc Viếng Bà Chúa Xứ Núi Sam</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>thuê xe đi Châu Đốc</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-di-chau-doc-an-giang.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Thuê Xe Carnival City Tour Sài Gòn 1 Ngày: Lịch Trình Cho Gia Đình Và Khách Nước Ngoài</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>thuê xe city tour Sài Gòn</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>thue-xe-carnival-city-tour-sai-gon.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Thuê Xe Có Tài Xế Đưa Đón Ông Bà, Người Lớn Tuổi Đi Khám Bệnh Tại TP.HCM</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>thuê xe đưa người già đi khám bệnh</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Dịch vụ đặc biệt</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>thue-xe-carnival-dua-don-nguoi-gia-di-kham-benh.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cách Tính Phí Phát Sinh Khi Thuê Xe Có Tài Xế: Vượt Giờ, Vượt Km, Cầu Đường</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>phí phát sinh thuê xe có tài xế</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Bảng giá</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>cach-tinh-phi-phat-sinh-thue-xe-co-tai-xe.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>So Sánh Kia Carnival Với Innova, Fortuner, Xpander Khi Thuê Xe 7 Chỗ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>nên thuê Carnival hay Innova Fortuner</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>so-sanh-kia-carnival-voi-cac-dong-xe-7-cho.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Thuê Xe Carnival Theo Giờ Tại TP.HCM: 6 Tình Huống Nên Dùng Để Tiết Kiệm</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>thuê xe 7 chỗ theo giờ TP.HCM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>khi-nao-nen-thue-xe-carnival-theo-gio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Thuê Xe 7 Chỗ Đi Long Hải – Hồ Tràm Cuối Tuần</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>thuê xe 7 chỗ đi Long Hải Hồ Tràm</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-di-long-hai-ho-tram.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Thuê Xe Carnival Đi Sóc Trăng: Chùa Khmer, Bánh Pía Và Lễ Hội Oóc Om Bóc</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>thuê xe 7 chỗ đi Sóc Trăng</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-di-soc-trang.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Thuê Xe Carnival Đi Vĩnh Long: Cù Lao An Bình, Làng Gốm Mang Thít</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>thuê xe 7 chỗ đi Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Đã đăng</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-di-vinh-long.html</t>
         </is>
       </c>
     </row>

--- a/Lich_Dang_Bai_SEO_ThueXeCarnival.xlsx
+++ b/Lich_Dang_Bai_SEO_ThueXeCarnival.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1782,6 +1782,376 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>kinh-nghiem-thue-xe-di-vinh-long.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Điểm Đón Xe Sân Bay Tân Sơn Nhất Ở Đâu? Hướng Dẫn Ga T1, T2, T3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>điểm đón xe sân bay Tân Sơn Nhất</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Đã viết - chưa đăng</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>diem-don-xe-san-bay-tan-son-nhat.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Thuê Xe 7 Chỗ Đi Sân Bay Long Thành: Quãng Đường, Thời Gian Và Lưu Ý</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>thuê xe đi sân bay Long Thành</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Đã viết - chưa đăng</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>thue-xe-di-san-bay-long-thanh.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Thuê Xe Tự Lái Đi Vũng Tàu: Chi Phí, Lộ Trình Và Kinh Nghiệm Giữ Cọc</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>thuê xe tự lái đi Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm thuê xe</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Đã viết - chưa đăng</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>thue-xe-tu-lai-di-vung-tau.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kinh Nghiệm Tự Lái Xe 7 Chỗ Đi Đà Lạt: Đèo Bảo Lộc, Điểm Nghỉ Và Định Mức Km</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>kinh nghiệm tự lái xe đi Đà Lạt</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm thuê xe</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Đã viết - chưa đăng</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-tu-lai-xe-di-da-lat.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Thuê Xe 7 Chỗ Đi Địa Đạo Củ Chi Trong Ngày: Lịch Trình Và Chi Phí</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>thuê xe đi địa đạo Củ Chi</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Đã viết - chưa đăng</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>thue-xe-di-dia-dao-cu-chi.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Thuê Xe 7 Chỗ Đi Cần Giờ Trong Ngày: Rừng Sác, Đảo Khỉ Và Hải Sản</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>thuê xe đi Cần Giờ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Đã viết - chưa đăng</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>thue-xe-di-can-gio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Thuê Xe 7 Chỗ Đi Bình Dương: Đại Nam, Khu Công Nghiệp Và Công Tác</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>thuê xe 7 chỗ đi Bình Dương</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Đã viết - chưa đăng</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>thue-xe-7-cho-di-binh-duong.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Thuê Xe Đưa Đón Nhân Viên, Chuyên Gia Hằng Ngày: Theo Tháng Hay Theo Ngày?</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>thuê xe đưa đón nhân viên hằng ngày</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Đã viết - chưa đăng</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>thue-xe-dua-don-nhan-vien-hang-ngay.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Thuê Xe 7 Chỗ Đi Bảo Lộc: Đồi Chè, Thác Đambri Và Điểm Nghỉ Trên Đường Đà Lạt</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>thuê xe đi Bảo Lộc</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Mua ngay</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Kinh nghiệm du lịch</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Đã viết - chưa đăng</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>thue-xe-di-bao-loc.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Lần Đầu Thuê Xe 7 Chỗ Có Tài Xế Tại TP.HCM: Checklist 10 Điều Cần Hỏi</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>thuê xe 7 chỗ có tài xế lần đầu</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Tìm hiểu</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Hướng dẫn</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Đã viết - chưa đăng</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>kinh-nghiem-thue-xe-7-cho-co-tai-xe-lan-dau.html</t>
         </is>
       </c>
     </row>
